--- a/sample_data/02_Word标书模板/模板占位符说明.xlsx
+++ b/sample_data/02_Word标书模板/模板占位符说明.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>XX铁路工程XX段</t>
+          <t>北京地铁12号线电气火灾监控采购</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TD2026-001</t>
+          <t>EEBWTP2026-120（1）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -485,132 +485,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>{{tenderer}}</t>
+          <t>{{package_no}}</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>招标人</t>
+          <t>包件号</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XX铁路局集团有限公司</t>
+          <t>DLZM08</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>封面、投标函</t>
+          <t>封面</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>{{bidder}}</t>
+          <t>{{tenderer}}</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>投标人</t>
+          <t>采购人</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XX铁路工程有限公司</t>
+          <t>中铁电气化局集团有限公司城铁公司</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>封面</t>
+          <t>封面、投标函</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>{{bid_amount}}</t>
+          <t>{{bidder_name}}</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>投标总价</t>
+          <t>投标人</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>人民币捌仟万元整</t>
+          <t>和远智能科技股份有限公司</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>报价部分</t>
+          <t>封面</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>{{duration}}</t>
+          <t>{{bid_amount_upper}}</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>工期</t>
+          <t>投标总价大写</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>365日历天</t>
+          <t>人民币壹仟贰佰捌拾万元整</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>技术部分</t>
+          <t>报价部分</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>{{project_manager}}</t>
+          <t>{{bid_amount_lower}}</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>项目经理</t>
+          <t>投标总价小写</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>12800000.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人员部分</t>
+          <t>报价部分</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>{{warranty_period}}</t>
+          <t>{{project_manager}}</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>质保期</t>
+          <t>项目经理</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24个月</t>
+          <t>张方恒</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>商务部分</t>
+          <t>人员部分</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{{material_type}}</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>物资品种</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RTU及能管系统</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>模板3专用</t>
         </is>
       </c>
     </row>
